--- a/xls/square_un_16_tri3_10.xlsx
+++ b/xls/square_un_16_tri3_10.xlsx
@@ -456,12 +456,82 @@
         <v>10</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>165</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>340</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>97</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>480</v>
+      </c>
+      <c r="I8">
+        <v>-0.00020531867226607578</v>
+      </c>
+      <c r="J8">
+        <v>-0.7830052232652177</v>
+      </c>
+      <c r="K8">
+        <v>-0.09095726382156319</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>165</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>340</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>122</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>618</v>
+      </c>
+      <c r="I9">
+        <v>-0.0002238144724598572</v>
+      </c>
+      <c r="J9">
+        <v>-1.5844071791621386</v>
+      </c>
+      <c r="K9">
+        <v>-0.5231472159207136</v>
+      </c>
+    </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C10" t="s">
         <v>11</v>
@@ -473,22 +543,22 @@
         <v>12</v>
       </c>
       <c r="F10">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
       </c>
       <c r="H10">
-        <v>600</v>
+        <v>864</v>
       </c>
       <c r="I10">
-        <v>-0.9281866455397223</v>
+        <v>-0.00021324553716697397</v>
       </c>
       <c r="J10">
-        <v>-1.3174240513058475</v>
+        <v>-1.304346300060168</v>
       </c>
       <c r="K10">
-        <v>-0.5059671247349852</v>
+        <v>-0.05325053048422094</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -496,7 +566,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -508,22 +578,22 @@
         <v>12</v>
       </c>
       <c r="F11">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
       <c r="H11">
-        <v>726</v>
+        <v>906</v>
       </c>
       <c r="I11">
-        <v>-1.6737760279350553</v>
+        <v>-0.00020913455476231522</v>
       </c>
       <c r="J11">
-        <v>-1.6964601436414113</v>
+        <v>-1.1865294416729115</v>
       </c>
       <c r="K11">
-        <v>-0.7538214981820702</v>
+        <v>0.4637872933688912</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -531,7 +601,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
         <v>11</v>
@@ -543,22 +613,22 @@
         <v>12</v>
       </c>
       <c r="F12">
-        <v>169</v>
+        <v>209</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
       <c r="H12">
-        <v>864</v>
+        <v>1104</v>
       </c>
       <c r="I12">
-        <v>-2.1743789026623173</v>
+        <v>-0.00019964680561587096</v>
       </c>
       <c r="J12">
-        <v>-1.7857591700645838</v>
+        <v>-1.0337859688388613</v>
       </c>
       <c r="K12">
-        <v>-0.6466835774533213</v>
+        <v>1.1091023592072822</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -566,7 +636,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C13" t="s">
         <v>11</v>
@@ -578,22 +648,22 @@
         <v>12</v>
       </c>
       <c r="F13">
-        <v>196</v>
+        <v>238</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
       </c>
       <c r="H13">
-        <v>1014</v>
+        <v>1266</v>
       </c>
       <c r="I13">
-        <v>-1.9675108367980685</v>
+        <v>-0.00017713299505812987</v>
       </c>
       <c r="J13">
-        <v>-1.5708989492737409</v>
+        <v>-0.7679814659223011</v>
       </c>
       <c r="K13">
-        <v>-0.2587655647910268</v>
+        <v>1.6573692277034167</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -601,7 +671,7 @@
         <v>11</v>
       </c>
       <c r="B14">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -613,22 +683,22 @@
         <v>12</v>
       </c>
       <c r="F14">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
       <c r="H14">
-        <v>1176</v>
+        <v>1362</v>
       </c>
       <c r="I14">
-        <v>-1.8210940429413225</v>
+        <v>-0.00016211693186858782</v>
       </c>
       <c r="J14">
-        <v>-1.466693122313872</v>
+        <v>-0.6612842909955077</v>
       </c>
       <c r="K14">
-        <v>-0.08787240412722104</v>
+        <v>2.2082615051666696</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -636,7 +706,7 @@
         <v>11</v>
       </c>
       <c r="B15">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -648,22 +718,22 @@
         <v>12</v>
       </c>
       <c r="F15">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
       </c>
       <c r="H15">
-        <v>1350</v>
+        <v>1596</v>
       </c>
       <c r="I15">
-        <v>-1.4485436776029583</v>
+        <v>-0.00012635101098772125</v>
       </c>
       <c r="J15">
-        <v>-1.2219966261904667</v>
+        <v>-0.45046808957614454</v>
       </c>
       <c r="K15">
-        <v>0.23110055280519443</v>
+        <v>2.63994248332515</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -671,7 +741,7 @@
         <v>11</v>
       </c>
       <c r="B16">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -683,22 +753,22 @@
         <v>12</v>
       </c>
       <c r="F16">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
       </c>
       <c r="H16">
-        <v>1536</v>
+        <v>1842</v>
       </c>
       <c r="I16">
-        <v>-1.1256695742839558</v>
+        <v>-5.4349724031923863e-5</v>
       </c>
       <c r="J16">
-        <v>-0.9568857927357686</v>
+        <v>-0.17522368359128518</v>
       </c>
       <c r="K16">
-        <v>0.5611043815858199</v>
+        <v>3.3805311577372965</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -706,7 +776,7 @@
         <v>11</v>
       </c>
       <c r="B17">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -718,22 +788,22 @@
         <v>12</v>
       </c>
       <c r="F17">
-        <v>324</v>
+        <v>380</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
       </c>
       <c r="H17">
-        <v>1734</v>
+        <v>2070</v>
       </c>
       <c r="I17">
-        <v>-0.6742727697199322</v>
+        <v>-2.8878321997065e-7</v>
       </c>
       <c r="J17">
-        <v>-0.5525074379981146</v>
+        <v>-0.0006968293325959723</v>
       </c>
       <c r="K17">
-        <v>1.1743743169502574</v>
+        <v>2.762002459041381</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -741,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B18">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -753,22 +823,22 @@
         <v>12</v>
       </c>
       <c r="F18">
-        <v>361</v>
+        <v>435</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
       </c>
       <c r="H18">
-        <v>1944</v>
+        <v>2388</v>
       </c>
       <c r="I18">
-        <v>-0.3285920996401465</v>
+        <v>-6.305444869045159e-9</v>
       </c>
       <c r="J18">
-        <v>-0.30578935037383287</v>
+        <v>-1.2676160600839993e-5</v>
       </c>
       <c r="K18">
-        <v>2.1519171105469455</v>
+        <v>2.0041421103383827</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -776,7 +846,7 @@
         <v>11</v>
       </c>
       <c r="B19">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -788,22 +858,22 @@
         <v>12</v>
       </c>
       <c r="F19">
-        <v>400</v>
+        <v>485</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
       </c>
       <c r="H19">
-        <v>2166</v>
+        <v>2676</v>
       </c>
       <c r="I19">
-        <v>-0.01816528023687645</v>
+        <v>-2.225299425413915e-9</v>
       </c>
       <c r="J19">
-        <v>-0.017279656892915895</v>
+        <v>-4.03200474637194e-6</v>
       </c>
       <c r="K19">
-        <v>2.428049692863245</v>
+        <v>1.7473528449647049</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -811,7 +881,7 @@
         <v>11</v>
       </c>
       <c r="B20">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -823,22 +893,22 @@
         <v>12</v>
       </c>
       <c r="F20">
-        <v>441</v>
+        <v>564</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
       <c r="H20">
-        <v>2400</v>
+        <v>3138</v>
       </c>
       <c r="I20">
-        <v>2.2512879940159028e-5</v>
+        <v>-1.6067704798777378e-9</v>
       </c>
       <c r="J20">
-        <v>-1.8308673167864528e-5</v>
+        <v>-2.8664205863825304e-6</v>
       </c>
       <c r="K20">
-        <v>2.3609468615778018</v>
+        <v>1.6703877584739069</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -846,7 +916,7 @@
         <v>11</v>
       </c>
       <c r="B21">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -858,22 +928,22 @@
         <v>12</v>
       </c>
       <c r="F21">
-        <v>484</v>
+        <v>598</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
       <c r="H21">
-        <v>2646</v>
+        <v>3330</v>
       </c>
       <c r="I21">
-        <v>-4.441723059817231e-6</v>
+        <v>-1.2285779773425435e-9</v>
       </c>
       <c r="J21">
-        <v>-1.0932681041867759e-5</v>
+        <v>-2.27112772599724e-6</v>
       </c>
       <c r="K21">
-        <v>2.086694391985564</v>
+        <v>1.6229907395287642</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -881,7 +951,7 @@
         <v>11</v>
       </c>
       <c r="B22">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -893,22 +963,22 @@
         <v>12</v>
       </c>
       <c r="F22">
-        <v>529</v>
+        <v>668</v>
       </c>
       <c r="G22" t="s">
         <v>13</v>
       </c>
       <c r="H22">
-        <v>2904</v>
+        <v>3738</v>
       </c>
       <c r="I22">
-        <v>-3.5673857091379487e-6</v>
+        <v>-1.1187081468222277e-9</v>
       </c>
       <c r="J22">
-        <v>-5.942212908875896e-6</v>
+        <v>-2.059863101819456e-6</v>
       </c>
       <c r="K22">
-        <v>1.9232455492201748</v>
+        <v>1.602637298535038</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -916,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="B23">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
@@ -928,22 +998,22 @@
         <v>12</v>
       </c>
       <c r="F23">
-        <v>576</v>
+        <v>741</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
       <c r="H23">
-        <v>3174</v>
+        <v>4164</v>
       </c>
       <c r="I23">
-        <v>-3.3252823555183755e-6</v>
+        <v>-9.387660394119722e-10</v>
       </c>
       <c r="J23">
-        <v>-4.4352669279572155e-6</v>
+        <v>-1.7265538199971126e-6</v>
       </c>
       <c r="K23">
-        <v>1.8343360631232855</v>
+        <v>1.5637705599130198</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -951,7 +1021,7 @@
         <v>11</v>
       </c>
       <c r="B24">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C24" t="s">
         <v>11</v>
@@ -963,22 +1033,22 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <v>625</v>
+        <v>797</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
       <c r="H24">
-        <v>3456</v>
+        <v>4488</v>
       </c>
       <c r="I24">
-        <v>-2.711119546396173e-6</v>
+        <v>-9.751890736349354e-10</v>
       </c>
       <c r="J24">
-        <v>-3.4371564260284637e-6</v>
+        <v>-1.776050398335169e-6</v>
       </c>
       <c r="K24">
-        <v>1.7711422238140564</v>
+        <v>1.5690924995253275</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -986,7 +1056,7 @@
         <v>11</v>
       </c>
       <c r="B25">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -998,22 +1068,22 @@
         <v>12</v>
       </c>
       <c r="F25">
-        <v>676</v>
+        <v>861</v>
       </c>
       <c r="G25" t="s">
         <v>13</v>
       </c>
       <c r="H25">
-        <v>3750</v>
+        <v>4860</v>
       </c>
       <c r="I25">
-        <v>-2.429450765525334e-6</v>
+        <v>-8.997209988050653e-10</v>
       </c>
       <c r="J25">
-        <v>-3.0522309781853373e-6</v>
+        <v>-1.6555483355744664e-6</v>
       </c>
       <c r="K25">
-        <v>1.7418493605757606</v>
+        <v>1.5546142234495868</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1021,7 +1091,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C26" t="s">
         <v>11</v>
@@ -1033,22 +1103,22 @@
         <v>12</v>
       </c>
       <c r="F26">
-        <v>729</v>
+        <v>927</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
       </c>
       <c r="H26">
-        <v>4056</v>
+        <v>5244</v>
       </c>
       <c r="I26">
-        <v>-2.0276885090398713e-6</v>
+        <v>-8.709897297752583e-10</v>
       </c>
       <c r="J26">
-        <v>-2.6363110369611697e-6</v>
+        <v>-1.6029899647440208e-6</v>
       </c>
       <c r="K26">
-        <v>1.715965268998444</v>
+        <v>1.5473932578918412</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1056,7 +1126,7 @@
         <v>11</v>
       </c>
       <c r="B27">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C27" t="s">
         <v>11</v>
@@ -1068,22 +1138,22 @@
         <v>12</v>
       </c>
       <c r="F27">
-        <v>784</v>
+        <v>977</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
       <c r="H27">
-        <v>4374</v>
+        <v>5532</v>
       </c>
       <c r="I27">
-        <v>-1.7258730542699714e-6</v>
+        <v>-8.274006334942449e-10</v>
       </c>
       <c r="J27">
-        <v>-2.2429315213474635e-6</v>
+        <v>-1.5293413019268464e-6</v>
       </c>
       <c r="K27">
-        <v>1.6840341783289732</v>
+        <v>1.5381561445663512</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1091,7 +1161,7 @@
         <v>11</v>
       </c>
       <c r="B28">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -1103,22 +1173,22 @@
         <v>12</v>
       </c>
       <c r="F28">
-        <v>841</v>
+        <v>1034</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
       <c r="H28">
-        <v>4704</v>
+        <v>5862</v>
       </c>
       <c r="I28">
-        <v>-1.7820487655461461e-6</v>
+        <v>-8.269822600220839e-10</v>
       </c>
       <c r="J28">
-        <v>-2.140833025364652e-6</v>
+        <v>-1.5323050292536157e-6</v>
       </c>
       <c r="K28">
-        <v>1.6601852312586372</v>
+        <v>1.5386039787711885</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1126,7 +1196,7 @@
         <v>11</v>
       </c>
       <c r="B29">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C29" t="s">
         <v>11</v>
@@ -1138,22 +1208,22 @@
         <v>12</v>
       </c>
       <c r="F29">
-        <v>900</v>
+        <v>1085</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
       <c r="H29">
-        <v>5046</v>
+        <v>6156</v>
       </c>
       <c r="I29">
-        <v>-1.6892558787347912e-6</v>
+        <v>-8.053319029479425e-10</v>
       </c>
       <c r="J29">
-        <v>-1.9700231636057133e-6</v>
+        <v>-1.504152603333948e-6</v>
       </c>
       <c r="K29">
-        <v>1.6366584605642152</v>
+        <v>1.5353572817257708</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1161,7 +1231,7 @@
         <v>11</v>
       </c>
       <c r="B30">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
         <v>11</v>
@@ -1173,22 +1243,22 @@
         <v>12</v>
       </c>
       <c r="F30">
-        <v>961</v>
+        <v>1177</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
       <c r="H30">
-        <v>5400</v>
+        <v>6696</v>
       </c>
       <c r="I30">
-        <v>-1.671659493467701e-6</v>
+        <v>-8.047552351218747e-10</v>
       </c>
       <c r="J30">
-        <v>-1.8764302271075476e-6</v>
+        <v>-1.4914547045776058e-6</v>
       </c>
       <c r="K30">
-        <v>1.6181217561731218</v>
+        <v>1.5329703357697397</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1196,7 +1266,7 @@
         <v>11</v>
       </c>
       <c r="B31">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C31" t="s">
         <v>11</v>
@@ -1208,22 +1278,22 @@
         <v>12</v>
       </c>
       <c r="F31">
-        <v>1024</v>
+        <v>1243</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
       <c r="H31">
-        <v>5766</v>
+        <v>7080</v>
       </c>
       <c r="I31">
-        <v>-1.5496950192055455e-6</v>
+        <v>-7.584665523165434e-10</v>
       </c>
       <c r="J31">
-        <v>-1.7356295745096884e-6</v>
+        <v>-1.413903035760885e-6</v>
       </c>
       <c r="K31">
-        <v>1.600469285435326</v>
+        <v>1.5220031366377471</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1231,7 +1301,7 @@
         <v>11</v>
       </c>
       <c r="B32">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="C32" t="s">
         <v>11</v>
@@ -1243,22 +1313,22 @@
         <v>12</v>
       </c>
       <c r="F32">
-        <v>1089</v>
+        <v>1325</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
       <c r="H32">
-        <v>6144</v>
+        <v>7560</v>
       </c>
       <c r="I32">
-        <v>-1.4686429831769502e-6</v>
+        <v>-7.696835129944791e-10</v>
       </c>
       <c r="J32">
-        <v>-1.6515875600361278e-6</v>
+        <v>-1.4366944019913319e-6</v>
       </c>
       <c r="K32">
-        <v>1.5906953729473983</v>
+        <v>1.5254886999165018</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_un_16_tri3_10.xlsx
+++ b/xls/square_un_16_tri3_10.xlsx
@@ -482,13 +482,13 @@
         <v>480</v>
       </c>
       <c r="I8">
-        <v>-0.00020531867226607578</v>
+        <v>4.646931384804402</v>
       </c>
       <c r="J8">
-        <v>-0.7830052232652177</v>
+        <v>0.9104526899256398</v>
       </c>
       <c r="K8">
-        <v>-0.09095726382156319</v>
+        <v>1.198120355362074</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -517,13 +517,13 @@
         <v>618</v>
       </c>
       <c r="I9">
-        <v>-0.0002238144724598572</v>
+        <v>-0.38677970349164437</v>
       </c>
       <c r="J9">
-        <v>-1.5844071791621386</v>
+        <v>-1.098187983732625</v>
       </c>
       <c r="K9">
-        <v>-0.5231472159207136</v>
+        <v>-0.38016758896883385</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -552,13 +552,13 @@
         <v>864</v>
       </c>
       <c r="I10">
-        <v>-0.00021324553716697397</v>
+        <v>-2.038674317035982</v>
       </c>
       <c r="J10">
-        <v>-1.304346300060168</v>
+        <v>-1.8471712413040529</v>
       </c>
       <c r="K10">
-        <v>-0.05325053048422094</v>
+        <v>-0.8504366555053573</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -587,13 +587,13 @@
         <v>906</v>
       </c>
       <c r="I11">
-        <v>-0.00020913455476231522</v>
+        <v>-2.213490225215359</v>
       </c>
       <c r="J11">
-        <v>-1.1865294416729115</v>
+        <v>-1.801657636750026</v>
       </c>
       <c r="K11">
-        <v>0.4637872933688912</v>
+        <v>-0.7689313673263793</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1104</v>
       </c>
       <c r="I12">
-        <v>-0.00019964680561587096</v>
+        <v>-2.153044248423513</v>
       </c>
       <c r="J12">
-        <v>-1.0337859688388613</v>
+        <v>-1.7441672409452817</v>
       </c>
       <c r="K12">
-        <v>1.1091023592072822</v>
+        <v>-0.5064721364473568</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1266</v>
       </c>
       <c r="I13">
-        <v>-0.00017713299505812987</v>
+        <v>-1.9668240920580915</v>
       </c>
       <c r="J13">
-        <v>-0.7679814659223011</v>
+        <v>-1.6080501177915256</v>
       </c>
       <c r="K13">
-        <v>1.6573692277034167</v>
+        <v>-0.2108793911318785</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1362</v>
       </c>
       <c r="I14">
-        <v>-0.00016211693186858782</v>
+        <v>-1.9652562690555324</v>
       </c>
       <c r="J14">
-        <v>-0.6612842909955077</v>
+        <v>-1.619582312666996</v>
       </c>
       <c r="K14">
-        <v>2.2082615051666696</v>
+        <v>-0.251318735768421</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1596</v>
       </c>
       <c r="I15">
-        <v>-0.00012635101098772125</v>
+        <v>-1.5266466482407846</v>
       </c>
       <c r="J15">
-        <v>-0.45046808957614454</v>
+        <v>-1.3425580454831643</v>
       </c>
       <c r="K15">
-        <v>2.63994248332515</v>
+        <v>0.16985702267988298</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -762,13 +762,13 @@
         <v>1842</v>
       </c>
       <c r="I16">
-        <v>-5.4349724031923863e-5</v>
+        <v>-1.600665997648649</v>
       </c>
       <c r="J16">
-        <v>-0.17522368359128518</v>
+        <v>-1.4882743898879618</v>
       </c>
       <c r="K16">
-        <v>3.3805311577372965</v>
+        <v>-0.1716217704143971</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2070</v>
       </c>
       <c r="I17">
-        <v>-2.8878321997065e-7</v>
+        <v>-0.25622039736664415</v>
       </c>
       <c r="J17">
-        <v>-0.0006968293325959723</v>
+        <v>-0.23058636655754203</v>
       </c>
       <c r="K17">
-        <v>2.762002459041381</v>
+        <v>1.8403339621500705</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -832,13 +832,13 @@
         <v>2388</v>
       </c>
       <c r="I18">
-        <v>-6.305444869045159e-9</v>
+        <v>-1.5725285659131975e-5</v>
       </c>
       <c r="J18">
-        <v>-1.2676160600839993e-5</v>
+        <v>-2.7073872188573114e-5</v>
       </c>
       <c r="K18">
-        <v>2.0041421103383827</v>
+        <v>2.263027674928857</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -867,13 +867,13 @@
         <v>2676</v>
       </c>
       <c r="I19">
-        <v>-2.225299425413915e-9</v>
+        <v>-4.332375759368363e-6</v>
       </c>
       <c r="J19">
-        <v>-4.03200474637194e-6</v>
+        <v>-5.556357575931422e-6</v>
       </c>
       <c r="K19">
-        <v>1.7473528449647049</v>
+        <v>1.8859136293055354</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -902,13 +902,13 @@
         <v>3138</v>
       </c>
       <c r="I20">
-        <v>-1.6067704798777378e-9</v>
+        <v>-2.310747155617766e-6</v>
       </c>
       <c r="J20">
-        <v>-2.8664205863825304e-6</v>
+        <v>-3.0375443805349028e-6</v>
       </c>
       <c r="K20">
-        <v>1.6703877584739069</v>
+        <v>1.7528467576998217</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -937,13 +937,13 @@
         <v>3330</v>
       </c>
       <c r="I21">
-        <v>-1.2285779773425435e-9</v>
+        <v>-1.9666236715531633e-6</v>
       </c>
       <c r="J21">
-        <v>-2.27112772599724e-6</v>
+        <v>-2.5447503268600114e-6</v>
       </c>
       <c r="K21">
-        <v>1.6229907395287642</v>
+        <v>1.7118556520272943</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -972,13 +972,13 @@
         <v>3738</v>
       </c>
       <c r="I22">
-        <v>-1.1187081468222277e-9</v>
+        <v>-1.6204449355999412e-6</v>
       </c>
       <c r="J22">
-        <v>-2.059863101819456e-6</v>
+        <v>-2.1070150478077026e-6</v>
       </c>
       <c r="K22">
-        <v>1.602637298535038</v>
+        <v>1.669751982710135</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>4164</v>
       </c>
       <c r="I23">
-        <v>-9.387660394119722e-10</v>
+        <v>-1.5985834745872859e-6</v>
       </c>
       <c r="J23">
-        <v>-1.7265538199971126e-6</v>
+        <v>-1.8955604649343335e-6</v>
       </c>
       <c r="K23">
-        <v>1.5637705599130198</v>
+        <v>1.6309519015704466</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>4488</v>
       </c>
       <c r="I24">
-        <v>-9.751890736349354e-10</v>
+        <v>-1.6743803096332506e-6</v>
       </c>
       <c r="J24">
-        <v>-1.776050398335169e-6</v>
+        <v>-1.9053259138277573e-6</v>
       </c>
       <c r="K24">
-        <v>1.5690924995253275</v>
+        <v>1.6250861309814713</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1077,13 +1077,13 @@
         <v>4860</v>
       </c>
       <c r="I25">
-        <v>-8.997209988050653e-10</v>
+        <v>-1.5903842723796672e-6</v>
       </c>
       <c r="J25">
-        <v>-1.6555483355744664e-6</v>
+        <v>-1.7838703277722014e-6</v>
       </c>
       <c r="K25">
-        <v>1.5546142234495868</v>
+        <v>1.6064607361244474</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>5244</v>
       </c>
       <c r="I26">
-        <v>-8.709897297752583e-10</v>
+        <v>-1.5057235989448473e-6</v>
       </c>
       <c r="J26">
-        <v>-1.6029899647440208e-6</v>
+        <v>-1.7238261532327024e-6</v>
       </c>
       <c r="K26">
-        <v>1.5473932578918412</v>
+        <v>1.6029134855689406</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>5532</v>
       </c>
       <c r="I27">
-        <v>-8.274006334942449e-10</v>
+        <v>-1.4826054555368806e-6</v>
       </c>
       <c r="J27">
-        <v>-1.5293413019268464e-6</v>
+        <v>-1.6520987317195136e-6</v>
       </c>
       <c r="K27">
-        <v>1.5381561445663512</v>
+        <v>1.5883536889580496</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1182,13 +1182,13 @@
         <v>5862</v>
       </c>
       <c r="I28">
-        <v>-8.269822600220839e-10</v>
+        <v>-1.5102625829227744e-6</v>
       </c>
       <c r="J28">
-        <v>-1.5323050292536157e-6</v>
+        <v>-1.6592530245256314e-6</v>
       </c>
       <c r="K28">
-        <v>1.5386039787711885</v>
+        <v>1.5862660362232102</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>6156</v>
       </c>
       <c r="I29">
-        <v>-8.053319029479425e-10</v>
+        <v>-1.541553309785608e-6</v>
       </c>
       <c r="J29">
-        <v>-1.504152603333948e-6</v>
+        <v>-1.66601114055331e-6</v>
       </c>
       <c r="K29">
-        <v>1.5353572817257708</v>
+        <v>1.5834030350520785</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1252,13 +1252,13 @@
         <v>6696</v>
       </c>
       <c r="I30">
-        <v>-8.047552351218747e-10</v>
+        <v>-1.4650552325716824e-6</v>
       </c>
       <c r="J30">
-        <v>-1.4914547045776058e-6</v>
+        <v>-1.6049007539370318e-6</v>
       </c>
       <c r="K30">
-        <v>1.5329703357697397</v>
+        <v>1.5785344909849521</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1287,13 +1287,13 @@
         <v>7080</v>
       </c>
       <c r="I31">
-        <v>-7.584665523165434e-10</v>
+        <v>-1.418442542989282e-6</v>
       </c>
       <c r="J31">
-        <v>-1.413903035760885e-6</v>
+        <v>-1.5381114339230415e-6</v>
       </c>
       <c r="K31">
-        <v>1.5220031366377471</v>
+        <v>1.5668058115594954</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1322,13 +1322,13 @@
         <v>7560</v>
       </c>
       <c r="I32">
-        <v>-7.696835129944791e-10</v>
+        <v>-1.4330106625147498e-6</v>
       </c>
       <c r="J32">
-        <v>-1.4366944019913319e-6</v>
+        <v>-1.5521658249227497e-6</v>
       </c>
       <c r="K32">
-        <v>1.5254886999165018</v>
+        <v>1.568357670088316</v>
       </c>
     </row>
   </sheetData>
